--- a/docs/combat/CHARACTER_LEVEL_PROGRESS.xlsx
+++ b/docs/combat/CHARACTER_LEVEL_PROGRESS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="104">
   <si>
     <t>FRACTURED CHORUS - STAT PROGRESS Lv1-18 (Optimal Build)</t>
   </si>
@@ -52,16 +52,16 @@
     <t>REN - DPS - Melody</t>
   </si>
   <si>
-    <t>HP: HP = STR * 2.0 + 30  |  Guard: min(EN * 2.5, 65%)  |  Dmg: Physical</t>
+    <t>HP: HP = STR * 2.0 + 30  |  Dmg: Physical</t>
   </si>
   <si>
     <t>HP</t>
   </si>
   <si>
-    <t>Guard %</t>
-  </si>
-  <si>
-    <t>AV</t>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Latency</t>
   </si>
   <si>
     <t>Luck</t>
@@ -82,7 +82,7 @@
     <t>x1.15</t>
   </si>
   <si>
-    <t>Strike (Basic), Guard (Guard) + Strike (Basic) + Guard</t>
+    <t>Strike (Basic) + Strike (Basic)</t>
   </si>
   <si>
     <t>9%</t>
@@ -103,7 +103,7 @@
     <t>x1.18</t>
   </si>
   <si>
-    <t>Riposte (Sig A) + Riposte (Sig A)</t>
+    <t>Riposte (Counter) + Riposte (Counter)</t>
   </si>
   <si>
     <t>x1.2</t>
@@ -136,7 +136,7 @@
     <t>x1.28</t>
   </si>
   <si>
-    <t>Finale (Sig B) + Finale (Sig B)</t>
+    <t>Finale (Burst) + Finale (Burst)</t>
   </si>
   <si>
     <t>16%</t>
@@ -181,10 +181,7 @@
     <t>CHARLOTTE - TANK - Rhythm</t>
   </si>
   <si>
-    <t>HP: HP = STR * 6.0 + 50  |  Parry: min(EN * 3.0, 75%)  |  Dmg: Physical</t>
-  </si>
-  <si>
-    <t>Parry %</t>
+    <t>HP: HP = STR * 6.0 + 50  |  Dmg: Physical</t>
   </si>
   <si>
     <t>3%</t>
@@ -193,7 +190,7 @@
     <t>x1.05</t>
   </si>
   <si>
-    <t>Ram (Basic), Parry (Guard) + Ram (Basic) + Parry (Guard)</t>
+    <t>Ram (Basic) + Ram (Basic)</t>
   </si>
   <si>
     <t>4%</t>
@@ -202,7 +199,7 @@
     <t>x1.06</t>
   </si>
   <si>
-    <t>Bulwark (Sig A) + Bulwark (Sig A)</t>
+    <t>Bulwark (Counter) + Bulwark (Counter)</t>
   </si>
   <si>
     <t>5%</t>
@@ -220,7 +217,7 @@
     <t>x1.1</t>
   </si>
   <si>
-    <t>Hold the Line (Sig B) + Hold the Line (Sig B)</t>
+    <t>Hold the Line (Support) + Hold the Line (Support)</t>
   </si>
   <si>
     <t>7%</t>
@@ -238,16 +235,13 @@
     <t>CODA - SUPPORT - Harmony</t>
   </si>
   <si>
-    <t>HP: HP = STR * 2.0 + Ma * 0.35 + 15  |  Ward: min(EN * 2 + Ma * 0.5, 55%)  |  Dmg: Magical</t>
-  </si>
-  <si>
-    <t>Ward %</t>
-  </si>
-  <si>
-    <t>Pulse (Basic), Ward (Guard) + Pulse (Basic) + Ward (Guard)</t>
-  </si>
-  <si>
-    <t>Arc (Sig A) + Arc (Sig A)</t>
+    <t>HP: HP = STR * 2.0 + Ma * 0.35 + 15  |  Dmg: Magical</t>
+  </si>
+  <si>
+    <t>Pulse (Basic) + Pulse (Basic)</t>
+  </si>
+  <si>
+    <t>Arc (Counter) + Arc (Counter)</t>
   </si>
   <si>
     <t>x1.19</t>
@@ -259,7 +253,7 @@
     <t>x1.25</t>
   </si>
   <si>
-    <t>Cadence (Sig B) + Cadence (Sig B)</t>
+    <t>Cadence (Support) + Cadence (Support)</t>
   </si>
   <si>
     <t>x1.27</t>
@@ -283,34 +277,34 @@
     <t>Coda</t>
   </si>
   <si>
-    <t>Strike (Basic) + Guard</t>
-  </si>
-  <si>
-    <t>Ram (Basic) + Parry (Guard)</t>
-  </si>
-  <si>
-    <t>Pulse (Basic) + Ward (Guard)</t>
+    <t>Strike (Basic)</t>
+  </si>
+  <si>
+    <t>Ram (Basic)</t>
+  </si>
+  <si>
+    <t>Pulse (Basic)</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>Bulwark (Sig A)</t>
-  </si>
-  <si>
-    <t>Riposte (Sig A)</t>
-  </si>
-  <si>
-    <t>Arc (Sig A)</t>
-  </si>
-  <si>
-    <t>Hold the Line (Sig B)</t>
-  </si>
-  <si>
-    <t>Finale (Sig B)</t>
-  </si>
-  <si>
-    <t>Cadence (Sig B)</t>
+    <t>Bulwark (Counter)</t>
+  </si>
+  <si>
+    <t>Riposte (Counter)</t>
+  </si>
+  <si>
+    <t>Arc (Counter)</t>
+  </si>
+  <si>
+    <t>Hold the Line (Support)</t>
+  </si>
+  <si>
+    <t>Finale (Burst)</t>
+  </si>
+  <si>
+    <t>Cadence (Support)</t>
   </si>
   <si>
     <t>PARTY HP BY LEVEL (auto-growth only)</t>
@@ -322,31 +316,19 @@
     <t>HB CONVERSION - 1 POINT = +5 HB</t>
   </si>
   <si>
-    <t>HB Before</t>
-  </si>
-  <si>
-    <t>AV (+1)</t>
-  </si>
-  <si>
-    <t>AV (+5)</t>
-  </si>
-  <si>
-    <t>Shift</t>
-  </si>
-  <si>
     <t>Meaning</t>
   </si>
   <si>
-    <t>0.8s faster</t>
-  </si>
-  <si>
-    <t>0.7s faster</t>
-  </si>
-  <si>
-    <t>0.5s faster</t>
-  </si>
-  <si>
-    <t>0.4s faster</t>
+    <t>Charlotte Lv15 optimal</t>
+  </si>
+  <si>
+    <t>Coda Lv15 optimal</t>
+  </si>
+  <si>
+    <t>Ren Lv15 optimal</t>
+  </si>
+  <si>
+    <t>Ren high HB build</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +1635,7 @@
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -1749,10 +1731,10 @@
         <v>74</v>
       </c>
       <c r="G4" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5">
-        <v>82.8</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>19</v>
@@ -1787,10 +1769,10 @@
         <v>76</v>
       </c>
       <c r="G5" s="4">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4">
-        <v>82.5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>22</v>
@@ -1825,10 +1807,10 @@
         <v>78</v>
       </c>
       <c r="G6" s="5">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5">
-        <v>82.2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>24</v>
@@ -1863,10 +1845,10 @@
         <v>82</v>
       </c>
       <c r="G7" s="5">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5">
-        <v>81.9</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>26</v>
@@ -1901,10 +1883,10 @@
         <v>86</v>
       </c>
       <c r="G8" s="5">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="H8" s="5">
-        <v>81.6</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>26</v>
@@ -1939,10 +1921,10 @@
         <v>88</v>
       </c>
       <c r="G9" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H9" s="4">
-        <v>78.7</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>30</v>
@@ -1977,10 +1959,10 @@
         <v>92</v>
       </c>
       <c r="G10" s="4">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="H10" s="4">
-        <v>78.4</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>32</v>
@@ -2015,10 +1997,10 @@
         <v>94</v>
       </c>
       <c r="G11" s="4">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="H11" s="4">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>34</v>
@@ -2053,10 +2035,10 @@
         <v>96</v>
       </c>
       <c r="G12" s="5">
-        <v>21.5</v>
+        <v>8</v>
       </c>
       <c r="H12" s="5">
-        <v>77.9</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>34</v>
@@ -2091,10 +2073,10 @@
         <v>100</v>
       </c>
       <c r="G13" s="5">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H13" s="5">
-        <v>77.7</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>37</v>
@@ -2129,10 +2111,10 @@
         <v>102</v>
       </c>
       <c r="G14" s="5">
-        <v>22.5</v>
+        <v>8</v>
       </c>
       <c r="H14" s="5">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>40</v>
@@ -2167,10 +2149,10 @@
         <v>104</v>
       </c>
       <c r="G15" s="4">
-        <v>25.5</v>
+        <v>8</v>
       </c>
       <c r="H15" s="4">
-        <v>74.8</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>40</v>
@@ -2205,10 +2187,10 @@
         <v>108</v>
       </c>
       <c r="G16" s="4">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H16" s="4">
-        <v>74.5</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>43</v>
@@ -2243,10 +2225,10 @@
         <v>112</v>
       </c>
       <c r="G17" s="4">
-        <v>26.5</v>
+        <v>8</v>
       </c>
       <c r="H17" s="4">
-        <v>74.3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>43</v>
@@ -2281,10 +2263,10 @@
         <v>114</v>
       </c>
       <c r="G18" s="5">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H18" s="5">
-        <v>71.9</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>46</v>
@@ -2319,10 +2301,10 @@
         <v>116</v>
       </c>
       <c r="G19" s="4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H19" s="4">
-        <v>71.6</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>48</v>
@@ -2357,10 +2339,10 @@
         <v>120</v>
       </c>
       <c r="G20" s="4">
-        <v>30.5</v>
+        <v>8</v>
       </c>
       <c r="H20" s="4">
-        <v>71.4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>48</v>
@@ -2395,10 +2377,10 @@
         <v>122</v>
       </c>
       <c r="G21" s="5">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H21" s="5">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>51</v>
@@ -2433,7 +2415,7 @@
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -2491,7 +2473,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -2529,22 +2511,22 @@
         <v>140</v>
       </c>
       <c r="G4" s="5">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5">
-        <v>114.3</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2567,16 +2549,16 @@
         <v>146</v>
       </c>
       <c r="G5" s="4">
-        <v>30.900000000000002</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4">
-        <v>113.7</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -2605,22 +2587,22 @@
         <v>152</v>
       </c>
       <c r="G6" s="5">
-        <v>34.8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5">
-        <v>113.2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="K6" s="5">
         <v>2</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2643,16 +2625,16 @@
         <v>164</v>
       </c>
       <c r="G7" s="5">
-        <v>35.7</v>
+        <v>7</v>
       </c>
       <c r="H7" s="5">
-        <v>112.7</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="K7" s="5">
         <v>3</v>
@@ -2681,16 +2663,16 @@
         <v>176</v>
       </c>
       <c r="G8" s="5">
-        <v>36.599999999999994</v>
+        <v>7</v>
       </c>
       <c r="H8" s="5">
-        <v>112.1</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="K8" s="5">
         <v>4</v>
@@ -2719,16 +2701,16 @@
         <v>182</v>
       </c>
       <c r="G9" s="4">
-        <v>37.5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4">
-        <v>106.7</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
@@ -2757,16 +2739,16 @@
         <v>194</v>
       </c>
       <c r="G10" s="4">
-        <v>38.400000000000006</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4">
-        <v>106.2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K10" s="4">
         <v>6</v>
@@ -2795,16 +2777,16 @@
         <v>200</v>
       </c>
       <c r="G11" s="4">
-        <v>42.3</v>
+        <v>7</v>
       </c>
       <c r="H11" s="4">
-        <v>105.7</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K11" s="4">
         <v>7</v>
@@ -2833,22 +2815,22 @@
         <v>206</v>
       </c>
       <c r="G12" s="5">
-        <v>46.2</v>
+        <v>7</v>
       </c>
       <c r="H12" s="5">
-        <v>105.3</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="K12" s="5">
         <v>8</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2871,16 +2853,16 @@
         <v>218</v>
       </c>
       <c r="G13" s="5">
-        <v>47.099999999999994</v>
+        <v>7</v>
       </c>
       <c r="H13" s="5">
-        <v>104.8</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
@@ -2909,16 +2891,16 @@
         <v>224</v>
       </c>
       <c r="G14" s="5">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H14" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="K14" s="5">
         <v>10</v>
@@ -2947,16 +2929,16 @@
         <v>230</v>
       </c>
       <c r="G15" s="4">
-        <v>51.900000000000006</v>
+        <v>7</v>
       </c>
       <c r="H15" s="4">
-        <v>99.6</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K15" s="4">
         <v>11</v>
@@ -2985,16 +2967,16 @@
         <v>242</v>
       </c>
       <c r="G16" s="4">
-        <v>52.800000000000004</v>
+        <v>7</v>
       </c>
       <c r="H16" s="4">
-        <v>99.2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" s="4">
         <v>12</v>
@@ -3023,16 +3005,16 @@
         <v>254</v>
       </c>
       <c r="G17" s="4">
-        <v>53.699999999999996</v>
+        <v>7</v>
       </c>
       <c r="H17" s="4">
-        <v>98.8</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K17" s="4">
         <v>13</v>
@@ -3061,10 +3043,10 @@
         <v>260</v>
       </c>
       <c r="G18" s="5">
-        <v>54.599999999999994</v>
+        <v>7</v>
       </c>
       <c r="H18" s="5">
-        <v>94.5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>19</v>
@@ -3099,10 +3081,10 @@
         <v>266</v>
       </c>
       <c r="G19" s="4">
-        <v>58.5</v>
+        <v>7</v>
       </c>
       <c r="H19" s="4">
-        <v>94.1</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>22</v>
@@ -3137,10 +3119,10 @@
         <v>278</v>
       </c>
       <c r="G20" s="4">
-        <v>59.400000000000006</v>
+        <v>7</v>
       </c>
       <c r="H20" s="4">
-        <v>93.8</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>22</v>
@@ -3175,10 +3157,10 @@
         <v>284</v>
       </c>
       <c r="G21" s="5">
-        <v>60.300000000000004</v>
+        <v>7</v>
       </c>
       <c r="H21" s="5">
-        <v>89.9</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>22</v>
@@ -3213,7 +3195,7 @@
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -3221,7 +3203,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3237,7 +3219,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3271,7 +3253,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -3309,22 +3291,22 @@
         <v>38</v>
       </c>
       <c r="G4" s="5">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3347,16 +3329,16 @@
         <v>40</v>
       </c>
       <c r="G5" s="4">
-        <v>21.9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4">
-        <v>95.6</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3385,16 +3367,16 @@
         <v>43</v>
       </c>
       <c r="G6" s="5">
-        <v>25.3</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5">
-        <v>95.2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K6" s="5">
         <v>2</v>
@@ -3423,10 +3405,10 @@
         <v>45</v>
       </c>
       <c r="G7" s="5">
-        <v>26.2</v>
+        <v>7</v>
       </c>
       <c r="H7" s="5">
-        <v>94.9</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>22</v>
@@ -3461,10 +3443,10 @@
         <v>48</v>
       </c>
       <c r="G8" s="5">
-        <v>27.6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="5">
-        <v>94.5</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>24</v>
@@ -3476,7 +3458,7 @@
         <v>4</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3499,16 +3481,16 @@
         <v>50</v>
       </c>
       <c r="G9" s="4">
-        <v>28.5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4">
-        <v>90.6</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
@@ -3537,10 +3519,10 @@
         <v>52</v>
       </c>
       <c r="G10" s="4">
-        <v>29.4</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4">
-        <v>90.2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>26</v>
@@ -3575,16 +3557,16 @@
         <v>55</v>
       </c>
       <c r="G11" s="4">
-        <v>32.8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="4">
-        <v>89.9</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K11" s="4">
         <v>7</v>
@@ -3613,10 +3595,10 @@
         <v>57</v>
       </c>
       <c r="G12" s="5">
-        <v>35.7</v>
+        <v>7</v>
       </c>
       <c r="H12" s="5">
-        <v>89.6</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>30</v>
@@ -3651,16 +3633,16 @@
         <v>60</v>
       </c>
       <c r="G13" s="5">
-        <v>37.1</v>
+        <v>7</v>
       </c>
       <c r="H13" s="5">
-        <v>89.2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
@@ -3689,10 +3671,10 @@
         <v>62</v>
       </c>
       <c r="G14" s="5">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H14" s="5">
-        <v>85.7</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>34</v>
@@ -3704,7 +3686,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3727,16 +3709,16 @@
         <v>65</v>
       </c>
       <c r="G15" s="4">
-        <v>41.4</v>
+        <v>7</v>
       </c>
       <c r="H15" s="4">
-        <v>85.4</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K15" s="4">
         <v>11</v>
@@ -3765,10 +3747,10 @@
         <v>67</v>
       </c>
       <c r="G16" s="4">
-        <v>42.3</v>
+        <v>7</v>
       </c>
       <c r="H16" s="4">
-        <v>85.1</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>37</v>
@@ -3803,10 +3785,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="4">
-        <v>43.7</v>
+        <v>7</v>
       </c>
       <c r="H17" s="4">
-        <v>84.8</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>37</v>
@@ -3841,16 +3823,16 @@
         <v>73</v>
       </c>
       <c r="G18" s="5">
-        <v>44.6</v>
+        <v>8</v>
       </c>
       <c r="H18" s="5">
-        <v>81.6</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K18" s="5">
         <v>14</v>
@@ -3879,10 +3861,10 @@
         <v>75</v>
       </c>
       <c r="G19" s="4">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H19" s="4">
-        <v>81.4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>43</v>
@@ -3917,16 +3899,16 @@
         <v>78</v>
       </c>
       <c r="G20" s="4">
-        <v>48.9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="4">
-        <v>81.1</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>43</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K20" s="4">
         <v>16</v>
@@ -3955,10 +3937,10 @@
         <v>80</v>
       </c>
       <c r="G21" s="5">
-        <v>50.3</v>
+        <v>8</v>
       </c>
       <c r="H21" s="5">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>46</v>
@@ -3997,7 +3979,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4008,13 +3990,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4022,13 +4004,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4036,13 +4018,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4053,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>1</v>
@@ -4064,7 +4046,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>1</v>
@@ -4084,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4092,13 +4074,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4106,13 +4088,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4120,13 +4102,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4137,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>1</v>
@@ -4148,7 +4130,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>1</v>
@@ -4168,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4176,13 +4158,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4190,13 +4172,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4204,13 +4186,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -4218,13 +4200,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4232,13 +4214,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4246,13 +4228,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4260,13 +4242,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -4294,7 +4276,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4306,16 +4288,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4638,163 +4620,96 @@
   <sheetPr>
     <tabColor rgb="FF0F3460"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>127</v>
+      </c>
+      <c r="B3" s="4">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>147</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>167</v>
+      </c>
+      <c r="B5" s="4">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>172</v>
+      </c>
+      <c r="B6" s="4">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>100</v>
-      </c>
-      <c r="B3" s="4">
-        <v>119.2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>114.3</v>
-      </c>
-      <c r="D3" s="4">
-        <v>-4.9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>120</v>
-      </c>
-      <c r="B4" s="4">
-        <v>100</v>
-      </c>
-      <c r="C4" s="4">
-        <v>96</v>
-      </c>
-      <c r="D4" s="4">
-        <v>-4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>125</v>
-      </c>
-      <c r="B5" s="4">
-        <v>96</v>
-      </c>
-      <c r="C5" s="4">
-        <v>92.3</v>
-      </c>
-      <c r="D5" s="4">
-        <v>-3.7</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>140</v>
-      </c>
-      <c r="B6" s="4">
-        <v>85.7</v>
-      </c>
-      <c r="C6" s="4">
-        <v>82.8</v>
-      </c>
-      <c r="D6" s="4">
-        <v>-2.9</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>145</v>
-      </c>
-      <c r="B7" s="4">
-        <v>82.8</v>
-      </c>
-      <c r="C7" s="4">
-        <v>80</v>
-      </c>
-      <c r="D7" s="4">
-        <v>-2.8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>150</v>
-      </c>
-      <c r="B8" s="4">
-        <v>80</v>
-      </c>
-      <c r="C8" s="4">
-        <v>77.4</v>
-      </c>
-      <c r="D8" s="4">
-        <v>-2.6</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>170</v>
-      </c>
-      <c r="B9" s="4">
-        <v>70.6</v>
-      </c>
-      <c r="C9" s="4">
-        <v>68.6</v>
-      </c>
-      <c r="D9" s="4">
-        <v>-2</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/combat/CHARACTER_LEVEL_PROGRESS.xlsx
+++ b/docs/combat/CHARACTER_LEVEL_PROGRESS.xlsx
@@ -10,14 +10,15 @@
     <sheet sheetId="4" name="Coda" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Skill Unlock" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Party HP" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="HB Conversion" state="visible" r:id="rId10"/>
+    <sheet sheetId="7" name="Combat XP" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="HB Conversion" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="142">
   <si>
     <t>FRACTURED CHORUS - STAT PROGRESS Lv1-18 (Optimal Build)</t>
   </si>
@@ -73,6 +74,9 @@
     <t>Pts</t>
   </si>
   <si>
+    <t>Spent</t>
+  </si>
+  <si>
     <t>Skill Unlock</t>
   </si>
   <si>
@@ -82,7 +86,10 @@
     <t>x1.15</t>
   </si>
   <si>
-    <t>Strike (Basic) + Strike (Basic)</t>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Strike (Basic)</t>
   </si>
   <si>
     <t>9%</t>
@@ -91,19 +98,25 @@
     <t>x1.16</t>
   </si>
   <si>
+    <t>+1 EN</t>
+  </si>
+  <si>
     <t>10%</t>
   </si>
   <si>
     <t>x1.17</t>
   </si>
   <si>
+    <t>+1 STR</t>
+  </si>
+  <si>
     <t>11%</t>
   </si>
   <si>
     <t>x1.18</t>
   </si>
   <si>
-    <t>Riposte (Counter) + Riposte (Counter)</t>
+    <t>Crosscut (Skill)</t>
   </si>
   <si>
     <t>x1.2</t>
@@ -121,6 +134,9 @@
     <t>x1.23</t>
   </si>
   <si>
+    <t>+5 HB</t>
+  </si>
+  <si>
     <t>14%</t>
   </si>
   <si>
@@ -136,7 +152,7 @@
     <t>x1.28</t>
   </si>
   <si>
-    <t>Finale (Burst) + Finale (Burst)</t>
+    <t>Finale (Ult)</t>
   </si>
   <si>
     <t>16%</t>
@@ -190,7 +206,7 @@
     <t>x1.05</t>
   </si>
   <si>
-    <t>Ram (Basic) + Ram (Basic)</t>
+    <t>Ram (Basic)</t>
   </si>
   <si>
     <t>4%</t>
@@ -199,7 +215,7 @@
     <t>x1.06</t>
   </si>
   <si>
-    <t>Bulwark (Counter) + Bulwark (Counter)</t>
+    <t>Anchor (Skill)</t>
   </si>
   <si>
     <t>5%</t>
@@ -217,7 +233,7 @@
     <t>x1.1</t>
   </si>
   <si>
-    <t>Hold the Line (Support) + Hold the Line (Support)</t>
+    <t>Bulwark (Ult)</t>
   </si>
   <si>
     <t>7%</t>
@@ -238,10 +254,13 @@
     <t>HP: HP = STR * 2.0 + Ma * 0.35 + 15  |  Dmg: Magical</t>
   </si>
   <si>
-    <t>Pulse (Basic) + Pulse (Basic)</t>
-  </si>
-  <si>
-    <t>Arc (Counter) + Arc (Counter)</t>
+    <t>Pulse (Basic)</t>
+  </si>
+  <si>
+    <t>+1 Ma</t>
+  </si>
+  <si>
+    <t>Mend (Skill)</t>
   </si>
   <si>
     <t>x1.19</t>
@@ -253,7 +272,7 @@
     <t>x1.25</t>
   </si>
   <si>
-    <t>Cadence (Support) + Cadence (Support)</t>
+    <t>Encore (Ult)</t>
   </si>
   <si>
     <t>x1.27</t>
@@ -277,40 +296,136 @@
     <t>Coda</t>
   </si>
   <si>
-    <t>Strike (Basic)</t>
-  </si>
-  <si>
-    <t>Ram (Basic)</t>
-  </si>
-  <si>
-    <t>Pulse (Basic)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Bulwark (Counter)</t>
-  </si>
-  <si>
-    <t>Riposte (Counter)</t>
-  </si>
-  <si>
-    <t>Arc (Counter)</t>
-  </si>
-  <si>
-    <t>Hold the Line (Support)</t>
-  </si>
-  <si>
-    <t>Finale (Burst)</t>
-  </si>
-  <si>
-    <t>Cadence (Support)</t>
-  </si>
-  <si>
-    <t>PARTY HP BY LEVEL (auto-growth only)</t>
+    <t>PARTY HP BY LEVEL (optimal build)</t>
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>COMBAT XP CURVE · Soft target Lv15 · Soft-cap · Boss grant 12600</t>
+  </si>
+  <si>
+    <t>From→To</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>Cum to To</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>1→2</t>
+  </si>
+  <si>
+    <t>2→3</t>
+  </si>
+  <si>
+    <t>3→4</t>
+  </si>
+  <si>
+    <t>4→5</t>
+  </si>
+  <si>
+    <t>5→6</t>
+  </si>
+  <si>
+    <t>6→7</t>
+  </si>
+  <si>
+    <t>7→8</t>
+  </si>
+  <si>
+    <t>8→9</t>
+  </si>
+  <si>
+    <t>9→10</t>
+  </si>
+  <si>
+    <t>10→11</t>
+  </si>
+  <si>
+    <t>11→12</t>
+  </si>
+  <si>
+    <t>12→13</t>
+  </si>
+  <si>
+    <t>13→14</t>
+  </si>
+  <si>
+    <t>14→15</t>
+  </si>
+  <si>
+    <t>Soft target</t>
+  </si>
+  <si>
+    <t>15→16</t>
+  </si>
+  <si>
+    <t>Soft-cap start</t>
+  </si>
+  <si>
+    <t>16→17</t>
+  </si>
+  <si>
+    <t>17→18</t>
+  </si>
+  <si>
+    <t>Hard cap</t>
+  </si>
+  <si>
+    <t>Floor band</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Recommended Lv</t>
+  </si>
+  <si>
+    <t>1–3</t>
+  </si>
+  <si>
+    <t>1–4</t>
+  </si>
+  <si>
+    <t>4–6</t>
+  </si>
+  <si>
+    <t>4–7</t>
+  </si>
+  <si>
+    <t>7–9</t>
+  </si>
+  <si>
+    <t>7–10</t>
+  </si>
+  <si>
+    <t>10–12</t>
+  </si>
+  <si>
+    <t>10–13</t>
+  </si>
+  <si>
+    <t>13–15</t>
+  </si>
+  <si>
+    <t>Boss F16 grant</t>
+  </si>
+  <si>
+    <t>Σ 15→18</t>
+  </si>
+  <si>
+    <t>First clear only</t>
   </si>
   <si>
     <t>HB CONVERSION - 1 POINT = +5 HB</t>
@@ -930,7 +1045,7 @@
         <v>145.5</v>
       </c>
       <c r="E5" s="4">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="F5" s="4">
         <v>16</v>
@@ -942,7 +1057,7 @@
         <v>105.5</v>
       </c>
       <c r="I5" s="4">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="J5" s="4">
         <v>7</v>
@@ -954,7 +1069,7 @@
         <v>125.5</v>
       </c>
       <c r="M5" s="4">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -962,7 +1077,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5">
         <v>6.4</v>
@@ -974,7 +1089,7 @@
         <v>5.4</v>
       </c>
       <c r="F6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5">
         <v>5.2</v>
@@ -1003,7 +1118,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5">
         <v>6.6</v>
@@ -1015,7 +1130,7 @@
         <v>5.6</v>
       </c>
       <c r="F7" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="5">
         <v>5.3</v>
@@ -1030,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L7" s="5">
         <v>126.5</v>
@@ -1053,7 +1168,7 @@
         <v>147</v>
       </c>
       <c r="E8" s="5">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="F8" s="5">
         <v>21</v>
@@ -1065,7 +1180,7 @@
         <v>107</v>
       </c>
       <c r="I8" s="5">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="J8" s="5">
         <v>10</v>
@@ -1077,7 +1192,7 @@
         <v>127</v>
       </c>
       <c r="M8" s="5">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1085,40 +1200,40 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4">
         <v>7</v>
       </c>
       <c r="D9" s="4">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="E9" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="4">
         <v>5.5</v>
       </c>
       <c r="H9" s="4">
-        <v>112.5</v>
+        <v>107.5</v>
       </c>
       <c r="I9" s="4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J9" s="4">
         <v>11</v>
       </c>
       <c r="K9" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L9" s="4">
-        <v>132.5</v>
+        <v>127.5</v>
       </c>
       <c r="M9" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1135,7 +1250,7 @@
         <v>153</v>
       </c>
       <c r="E10" s="4">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="F10" s="4">
         <v>24</v>
@@ -1147,19 +1262,19 @@
         <v>113</v>
       </c>
       <c r="I10" s="4">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="J10" s="4">
         <v>12</v>
       </c>
       <c r="K10" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="4">
         <v>133</v>
       </c>
       <c r="M10" s="4">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1176,7 +1291,7 @@
         <v>153.5</v>
       </c>
       <c r="E11" s="4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F11" s="4">
         <v>25</v>
@@ -1188,7 +1303,7 @@
         <v>113.5</v>
       </c>
       <c r="I11" s="4">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="J11" s="4">
         <v>13</v>
@@ -1200,7 +1315,7 @@
         <v>133.5</v>
       </c>
       <c r="M11" s="4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1208,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5">
         <v>7.6</v>
@@ -1220,7 +1335,7 @@
         <v>8.6</v>
       </c>
       <c r="F12" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="5">
         <v>5.8</v>
@@ -1235,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L12" s="5">
         <v>134</v>
@@ -1255,7 +1370,7 @@
         <v>7.8</v>
       </c>
       <c r="D13" s="5">
-        <v>154.5</v>
+        <v>159.5</v>
       </c>
       <c r="E13" s="5">
         <v>8.8</v>
@@ -1267,7 +1382,7 @@
         <v>5.9</v>
       </c>
       <c r="H13" s="5">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="I13" s="5">
         <v>15.7</v>
@@ -1279,7 +1394,7 @@
         <v>43</v>
       </c>
       <c r="L13" s="5">
-        <v>134.5</v>
+        <v>139.5</v>
       </c>
       <c r="M13" s="5">
         <v>7.8</v>
@@ -1299,7 +1414,7 @@
         <v>160</v>
       </c>
       <c r="E14" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5">
         <v>29</v>
@@ -1311,7 +1426,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="5">
         <v>16</v>
@@ -1323,7 +1438,7 @@
         <v>140</v>
       </c>
       <c r="M14" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1331,7 +1446,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="4">
         <v>8.2</v>
@@ -1343,7 +1458,7 @@
         <v>10.2</v>
       </c>
       <c r="F15" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" s="4">
         <v>6.1</v>
@@ -1372,7 +1487,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4">
         <v>8.4</v>
@@ -1384,7 +1499,7 @@
         <v>10.4</v>
       </c>
       <c r="F16" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G16" s="4">
         <v>6.2</v>
@@ -1399,7 +1514,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L16" s="4">
         <v>141</v>
@@ -1422,7 +1537,7 @@
         <v>161.5</v>
       </c>
       <c r="E17" s="4">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F17" s="4">
         <v>34</v>
@@ -1434,7 +1549,7 @@
         <v>121.5</v>
       </c>
       <c r="I17" s="4">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="J17" s="4">
         <v>19</v>
@@ -1446,7 +1561,7 @@
         <v>141.5</v>
       </c>
       <c r="M17" s="4">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1463,7 +1578,7 @@
         <v>167</v>
       </c>
       <c r="E18" s="5">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="F18" s="5">
         <v>35</v>
@@ -1475,7 +1590,7 @@
         <v>127</v>
       </c>
       <c r="I18" s="5">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="J18" s="5">
         <v>20</v>
@@ -1487,7 +1602,7 @@
         <v>147</v>
       </c>
       <c r="M18" s="5">
-        <v>9.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1504,7 +1619,7 @@
         <v>167.5</v>
       </c>
       <c r="E19" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="4">
         <v>36</v>
@@ -1516,19 +1631,19 @@
         <v>127.5</v>
       </c>
       <c r="I19" s="4">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="J19" s="4">
         <v>21</v>
       </c>
       <c r="K19" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L19" s="4">
         <v>147.5</v>
       </c>
       <c r="M19" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1545,7 +1660,7 @@
         <v>168</v>
       </c>
       <c r="E20" s="4">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F20" s="4">
         <v>38</v>
@@ -1557,7 +1672,7 @@
         <v>128</v>
       </c>
       <c r="I20" s="4">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
       <c r="J20" s="4">
         <v>22</v>
@@ -1569,7 +1684,7 @@
         <v>148</v>
       </c>
       <c r="M20" s="4">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1586,7 +1701,7 @@
         <v>173.5</v>
       </c>
       <c r="E21" s="5">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="F21" s="5">
         <v>39</v>
@@ -1598,19 +1713,19 @@
         <v>133.5</v>
       </c>
       <c r="I21" s="5">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="J21" s="5">
         <v>23</v>
       </c>
       <c r="K21" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L21" s="5">
         <v>153.5</v>
       </c>
       <c r="M21" s="5">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>
@@ -1630,18 +1745,18 @@
   <sheetPr>
     <tabColor rgb="FFE94560"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="8" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1656,8 +1771,9 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -1672,8 +1788,9 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1710,8 +1827,11 @@
       <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1737,19 +1857,22 @@
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1763,7 +1886,7 @@
         <v>145.5</v>
       </c>
       <c r="E5" s="4">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="F5" s="4">
         <v>76</v>
@@ -1775,24 +1898,27 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5">
         <v>6.4</v>
@@ -1804,7 +1930,7 @@
         <v>5.4</v>
       </c>
       <c r="F6" s="5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" s="5">
         <v>8</v>
@@ -1813,24 +1939,27 @@
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5">
         <v>2</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5">
         <v>6.6</v>
@@ -1842,7 +1971,7 @@
         <v>5.6</v>
       </c>
       <c r="F7" s="5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7" s="5">
         <v>8</v>
@@ -1851,19 +1980,22 @@
         <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K7" s="5">
         <v>3</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1877,7 +2009,7 @@
         <v>147</v>
       </c>
       <c r="E8" s="5">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="F8" s="5">
         <v>86</v>
@@ -1889,36 +2021,39 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K8" s="5">
         <v>4</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4">
         <v>7</v>
       </c>
       <c r="D9" s="4">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="E9" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="4">
         <v>8</v>
@@ -1927,19 +2062,22 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -1953,7 +2091,7 @@
         <v>153</v>
       </c>
       <c r="E10" s="4">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="F10" s="4">
         <v>92</v>
@@ -1965,19 +2103,22 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K10" s="4">
         <v>6</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -1991,7 +2132,7 @@
         <v>153.5</v>
       </c>
       <c r="E11" s="4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F11" s="4">
         <v>94</v>
@@ -2003,24 +2144,27 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K11" s="4">
         <v>7</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5">
         <v>7.6</v>
@@ -2032,7 +2176,7 @@
         <v>8.6</v>
       </c>
       <c r="F12" s="5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" s="5">
         <v>8</v>
@@ -2041,19 +2185,22 @@
         <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K12" s="5">
         <v>8</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -2064,7 +2211,7 @@
         <v>7.8</v>
       </c>
       <c r="D13" s="5">
-        <v>154.5</v>
+        <v>159.5</v>
       </c>
       <c r="E13" s="5">
         <v>8.8</v>
@@ -2079,19 +2226,22 @@
         <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -2105,7 +2255,7 @@
         <v>160</v>
       </c>
       <c r="E14" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5">
         <v>102</v>
@@ -2117,24 +2267,27 @@
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K14" s="5">
         <v>10</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
       <c r="B15" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="4">
         <v>8.2</v>
@@ -2146,7 +2299,7 @@
         <v>10.2</v>
       </c>
       <c r="F15" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G15" s="4">
         <v>8</v>
@@ -2155,24 +2308,27 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K15" s="4">
         <v>11</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4">
         <v>8.4</v>
@@ -2184,7 +2340,7 @@
         <v>10.4</v>
       </c>
       <c r="F16" s="4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G16" s="4">
         <v>8</v>
@@ -2193,19 +2349,22 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K16" s="4">
         <v>12</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -2219,7 +2378,7 @@
         <v>161.5</v>
       </c>
       <c r="E17" s="4">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F17" s="4">
         <v>112</v>
@@ -2231,19 +2390,22 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K17" s="4">
         <v>13</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -2257,7 +2419,7 @@
         <v>167</v>
       </c>
       <c r="E18" s="5">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="F18" s="5">
         <v>114</v>
@@ -2269,19 +2431,22 @@
         <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K18" s="5">
         <v>14</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -2295,7 +2460,7 @@
         <v>167.5</v>
       </c>
       <c r="E19" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="4">
         <v>116</v>
@@ -2307,19 +2472,22 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K19" s="4">
         <v>15</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -2333,7 +2501,7 @@
         <v>168</v>
       </c>
       <c r="E20" s="4">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F20" s="4">
         <v>120</v>
@@ -2345,19 +2513,22 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K20" s="4">
         <v>16</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -2371,7 +2542,7 @@
         <v>173.5</v>
       </c>
       <c r="E21" s="5">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="F21" s="5">
         <v>122</v>
@@ -2383,22 +2554,25 @@
         <v>0</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K21" s="5">
         <v>17</v>
       </c>
       <c r="L21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2410,20 +2584,20 @@
   <sheetPr>
     <tabColor rgb="FF0F3460"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="8" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2436,10 +2610,11 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2452,8 +2627,9 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2490,8 +2666,11 @@
       <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -2517,19 +2696,22 @@
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -2543,7 +2725,7 @@
         <v>105.5</v>
       </c>
       <c r="E5" s="4">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="F5" s="4">
         <v>146</v>
@@ -2555,24 +2737,27 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5">
         <v>5.2</v>
@@ -2584,7 +2769,7 @@
         <v>11.6</v>
       </c>
       <c r="F6" s="5">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G6" s="5">
         <v>7</v>
@@ -2593,24 +2778,27 @@
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K6" s="5">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5">
         <v>5.3</v>
@@ -2622,7 +2810,7 @@
         <v>11.9</v>
       </c>
       <c r="F7" s="5">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G7" s="5">
         <v>7</v>
@@ -2631,19 +2819,22 @@
         <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K7" s="5">
         <v>3</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -2657,7 +2848,7 @@
         <v>107</v>
       </c>
       <c r="E8" s="5">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F8" s="5">
         <v>176</v>
@@ -2669,36 +2860,39 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K8" s="5">
         <v>4</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4">
         <v>5.5</v>
       </c>
       <c r="D9" s="4">
-        <v>112.5</v>
+        <v>107.5</v>
       </c>
       <c r="E9" s="4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="F9" s="4">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G9" s="4">
         <v>7</v>
@@ -2707,19 +2901,22 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -2733,7 +2930,7 @@
         <v>113</v>
       </c>
       <c r="E10" s="4">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F10" s="4">
         <v>194</v>
@@ -2745,19 +2942,22 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K10" s="4">
         <v>6</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -2771,7 +2971,7 @@
         <v>113.5</v>
       </c>
       <c r="E11" s="4">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="F11" s="4">
         <v>200</v>
@@ -2783,24 +2983,27 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K11" s="4">
         <v>7</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="5">
         <v>5.8</v>
@@ -2812,7 +3015,7 @@
         <v>15.4</v>
       </c>
       <c r="F12" s="5">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G12" s="5">
         <v>7</v>
@@ -2821,19 +3024,22 @@
         <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K12" s="5">
         <v>8</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -2844,7 +3050,7 @@
         <v>5.9</v>
       </c>
       <c r="D13" s="5">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="E13" s="5">
         <v>15.7</v>
@@ -2859,19 +3065,22 @@
         <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -2885,7 +3094,7 @@
         <v>120</v>
       </c>
       <c r="E14" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="5">
         <v>224</v>
@@ -2897,24 +3106,27 @@
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K14" s="5">
         <v>10</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
       <c r="B15" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4">
         <v>6.1</v>
@@ -2926,7 +3138,7 @@
         <v>17.3</v>
       </c>
       <c r="F15" s="4">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G15" s="4">
         <v>7</v>
@@ -2935,24 +3147,27 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K15" s="4">
         <v>11</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="4">
         <v>6.2</v>
@@ -2964,7 +3179,7 @@
         <v>17.6</v>
       </c>
       <c r="F16" s="4">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G16" s="4">
         <v>7</v>
@@ -2973,19 +3188,22 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K16" s="4">
         <v>12</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -2999,7 +3217,7 @@
         <v>121.5</v>
       </c>
       <c r="E17" s="4">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="F17" s="4">
         <v>254</v>
@@ -3011,19 +3229,22 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K17" s="4">
         <v>13</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -3037,7 +3258,7 @@
         <v>127</v>
       </c>
       <c r="E18" s="5">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="F18" s="5">
         <v>260</v>
@@ -3049,19 +3270,22 @@
         <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="5">
         <v>14</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -3075,7 +3299,7 @@
         <v>127.5</v>
       </c>
       <c r="E19" s="4">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="F19" s="4">
         <v>266</v>
@@ -3087,19 +3311,22 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K19" s="4">
         <v>15</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -3113,7 +3340,7 @@
         <v>128</v>
       </c>
       <c r="E20" s="4">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
       <c r="F20" s="4">
         <v>278</v>
@@ -3125,19 +3352,22 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" s="4">
         <v>16</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -3151,7 +3381,7 @@
         <v>133.5</v>
       </c>
       <c r="E21" s="5">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="F21" s="5">
         <v>284</v>
@@ -3163,22 +3393,25 @@
         <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K21" s="5">
         <v>17</v>
       </c>
       <c r="L21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3190,20 +3423,20 @@
   <sheetPr>
     <tabColor rgb="FF00D2FF"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="8" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3216,10 +3449,11 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3232,8 +3466,9 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3270,8 +3505,11 @@
       <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -3297,19 +3535,22 @@
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -3323,7 +3564,7 @@
         <v>125.5</v>
       </c>
       <c r="E5" s="4">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="F5" s="4">
         <v>40</v>
@@ -3335,19 +3576,22 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -3373,19 +3617,22 @@
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K6" s="5">
         <v>2</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -3393,7 +3640,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5">
         <v>126.5</v>
@@ -3411,19 +3658,22 @@
         <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="5">
         <v>3</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -3437,7 +3687,7 @@
         <v>127</v>
       </c>
       <c r="E8" s="5">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="F8" s="5">
         <v>48</v>
@@ -3449,19 +3699,22 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K8" s="5">
         <v>4</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -3469,13 +3722,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4">
-        <v>132.5</v>
+        <v>127.5</v>
       </c>
       <c r="E9" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="4">
         <v>50</v>
@@ -3487,19 +3740,22 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -3507,16 +3763,16 @@
         <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="4">
         <v>133</v>
       </c>
       <c r="E10" s="4">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="F10" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" s="4">
         <v>7</v>
@@ -3525,19 +3781,22 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K10" s="4">
         <v>6</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -3551,7 +3810,7 @@
         <v>133.5</v>
       </c>
       <c r="E11" s="4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="F11" s="4">
         <v>55</v>
@@ -3563,19 +3822,22 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K11" s="4">
         <v>7</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -3583,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5">
         <v>134</v>
@@ -3592,7 +3854,7 @@
         <v>7.6</v>
       </c>
       <c r="F12" s="5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="5">
         <v>7</v>
@@ -3601,19 +3863,22 @@
         <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K12" s="5">
         <v>8</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -3624,7 +3889,7 @@
         <v>43</v>
       </c>
       <c r="D13" s="5">
-        <v>134.5</v>
+        <v>139.5</v>
       </c>
       <c r="E13" s="5">
         <v>7.8</v>
@@ -3639,19 +3904,22 @@
         <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -3665,7 +3933,7 @@
         <v>140</v>
       </c>
       <c r="E14" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="5">
         <v>62</v>
@@ -3677,19 +3945,22 @@
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K14" s="5">
         <v>10</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -3715,19 +3986,22 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K15" s="4">
         <v>11</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -3735,7 +4009,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="4">
         <v>141</v>
@@ -3744,7 +4018,7 @@
         <v>9.4</v>
       </c>
       <c r="F16" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="4">
         <v>7</v>
@@ -3753,19 +4027,22 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K16" s="4">
         <v>12</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -3779,7 +4056,7 @@
         <v>141.5</v>
       </c>
       <c r="E17" s="4">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="F17" s="4">
         <v>70</v>
@@ -3791,19 +4068,22 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K17" s="4">
         <v>13</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -3817,7 +4097,7 @@
         <v>147</v>
       </c>
       <c r="E18" s="5">
-        <v>9.8</v>
+        <v>10.8</v>
       </c>
       <c r="F18" s="5">
         <v>73</v>
@@ -3829,19 +4109,22 @@
         <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K18" s="5">
         <v>14</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -3849,13 +4132,13 @@
         <v>21</v>
       </c>
       <c r="C19" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4">
         <v>147.5</v>
       </c>
       <c r="E19" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4">
         <v>75</v>
@@ -3867,19 +4150,22 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" s="4">
         <v>15</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -3893,7 +4179,7 @@
         <v>148</v>
       </c>
       <c r="E20" s="4">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="F20" s="4">
         <v>78</v>
@@ -3905,19 +4191,22 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K20" s="4">
         <v>16</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -3925,13 +4214,13 @@
         <v>23</v>
       </c>
       <c r="C21" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="5">
         <v>153.5</v>
       </c>
       <c r="E21" s="5">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F21" s="5">
         <v>80</v>
@@ -3943,22 +4232,25 @@
         <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K21" s="5">
         <v>17</v>
       </c>
       <c r="L21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3979,7 +4271,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3990,13 +4282,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4004,13 +4296,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4018,27 +4310,27 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>1</v>
+      <c r="B5" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4046,27 +4338,27 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
+      <c r="B7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4074,13 +4366,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4088,13 +4380,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4102,27 +4394,27 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>1</v>
+      <c r="B11" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4130,27 +4422,27 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>1</v>
+      <c r="B13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4158,13 +4450,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4172,13 +4464,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4186,13 +4478,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -4200,13 +4492,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4214,13 +4506,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4228,13 +4520,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4242,13 +4534,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4276,7 +4568,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4288,16 +4580,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4339,16 +4631,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D5" s="4">
         <v>43</v>
       </c>
       <c r="E5" s="4">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4356,16 +4648,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D6" s="4">
         <v>45</v>
       </c>
       <c r="E6" s="4">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4390,16 +4682,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D8" s="4">
         <v>50</v>
       </c>
       <c r="E8" s="4">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4413,10 +4705,10 @@
         <v>194</v>
       </c>
       <c r="D9" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="4">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4441,16 +4733,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" s="4">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D11" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="4">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4492,16 +4784,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D14" s="4">
         <v>65</v>
       </c>
       <c r="E14" s="4">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -4509,16 +4801,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C15" s="4">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D15" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="4">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -4590,19 +4882,19 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>122</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>284</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>80</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>486</v>
       </c>
     </row>
@@ -4616,6 +4908,387 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF2D6A4F"/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="4">
+        <v>60</v>
+      </c>
+      <c r="C3" s="4">
+        <v>60</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="4">
+        <v>90</v>
+      </c>
+      <c r="C4" s="4">
+        <v>150</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="4">
+        <v>130</v>
+      </c>
+      <c r="C5" s="4">
+        <v>280</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="4">
+        <v>180</v>
+      </c>
+      <c r="C6" s="4">
+        <v>460</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="4">
+        <v>240</v>
+      </c>
+      <c r="C7" s="4">
+        <v>700</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="4">
+        <v>310</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1010</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="4">
+        <v>390</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="4">
+        <v>480</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1880</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="4">
+        <v>580</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2460</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="4">
+        <v>690</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3150</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="4">
+        <v>810</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3960</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="4">
+        <v>940</v>
+      </c>
+      <c r="C14" s="4">
+        <v>4900</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1080</v>
+      </c>
+      <c r="C15" s="4">
+        <v>5980</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1230</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7210</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3600</v>
+      </c>
+      <c r="C17" s="5">
+        <v>10810</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="4">
+        <v>4200</v>
+      </c>
+      <c r="C18" s="4">
+        <v>15010</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="5">
+        <v>4800</v>
+      </c>
+      <c r="C19" s="5">
+        <v>19810</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="4">
+        <v>120</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="4">
+        <v>220</v>
+      </c>
+      <c r="C23" s="4">
+        <v>380</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="4">
+        <v>350</v>
+      </c>
+      <c r="C24" s="4">
+        <v>600</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="4">
+        <v>500</v>
+      </c>
+      <c r="C25" s="4">
+        <v>850</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="4">
+        <v>700</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="5">
+        <v>12600</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0F3460"/>
@@ -4631,7 +5304,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4648,7 +5321,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4662,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4676,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4690,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4704,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
